--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>31/08 13:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>31/08 14:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>31/08 17:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>150</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>31/08 15:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>125</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>31/08 13:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>125</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>31/08 14:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>110</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>85</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>31/08 10:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>31/08 19:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>60</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>31/08 17:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>31/08 13:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>100</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>31/08 12:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>01/09 00:15</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>06/09 16:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>75</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>04/09 18:45</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>65</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>31/08 16:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>60</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>31/08 17:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>31/08 19:45</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>50</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>31/08 14:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>31/08 21:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>45</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>31/08 16:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>15</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>01/09 14:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F23" t="n">
+        <v>1.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>01/09 15:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F24" t="n">
+        <v>3.5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>31/08 19:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F25" t="n">
+        <v>2.5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45900.07346611991</v>
+        <v>45900.07346612268</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,201 @@
           <t>05/09 18:45</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+11,8%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45900.07346612268</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mountfield HK – Brynäs IFEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>31/08 14:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+79,7%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45900.13076133841</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | T.Machac –</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>T.Machac – T.FritzATP - US Open H</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>31/08 19:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+42,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45900.13076133841</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – FK OleksandriaUPL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+40,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45900.13076133841</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cadix – Al</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cadix – AlbaceteLaLiga2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+11,8%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45900.07346611991</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+15,6%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45900.13076133841</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>31/08 14:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>125</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45900.13076133841</v>
+        <v>45900.1307613426</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>31/08 19:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45900.13076133841</v>
+        <v>45900.1307613426</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>55</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45900.13076133841</v>
+        <v>45900.1307613426</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>50</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,142 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45900.13076133841</v>
+        <v>45900.1307613426</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Salzbourg </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Salzbourg – Fischtown PinguinsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>31/08 15:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+97,8%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45900.18374988264</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Malmo FF –</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Malmo FF – Degerfors IFAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>31/08 12:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+45,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45900.18374988264</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Kashiwa Re</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol – Avispa FukuokaJ-League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>31/08 10:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+27,4%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45900.18374988264</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -1752,10 +1752,8 @@
           <t>31/08 15:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>140</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45900.18374988264</v>
+        <v>45900.18374988426</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>31/08 12:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>60</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45900.18374988264</v>
+        <v>45900.18374988426</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>31/08 10:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>55</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45900.18374988264</v>
+        <v>45900.18374988426</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,6 +1855,186 @@
         <v>45900.18374988426</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Hammarby I</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hammarby IF – Osters IFAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>31/08 14:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+36,4%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45900.27025079046</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 2 (−2.5) | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Alexander BublikUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>01/09 15:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,00%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+29,7%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45900.27025079046</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Grenade – </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Grenade – MirandesLaLiga2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>31/08 19:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+29,2%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45900.27025079046</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Las Palmas</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Las Palmas – MalagaLaLiga2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>31/08 17:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+16,3%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45900.27025079046</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>31/08 14:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>55</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45900.27025079046</v>
+        <v>45900.27025078703</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>01/09 15:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>65</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45900.27025079046</v>
+        <v>45900.27025078703</v>
       </c>
     </row>
     <row r="36">
@@ -1971,10 +1967,8 @@
           <t>31/08 19:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>55</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1987,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45900.27025079046</v>
+        <v>45900.27025078703</v>
       </c>
     </row>
     <row r="37">
@@ -2016,10 +2010,8 @@
           <t>31/08 17:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>50</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2032,7 +2024,52 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45900.27025079046</v>
+        <v>45900.27025078703</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Frolunda –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Frolunda – LausanneLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>31/08 13:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+50,8%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45900.30483301736</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>31/08 13:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>90</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,52 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45900.30483301736</v>
+        <v>45900.30483302083</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Ilves –</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FC Ilves – IFK MariehamnVeikkausliiga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>31/08 14:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+23,2%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45900.35040481629</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>31/08 14:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>50</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,52 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45900.35040481629</v>
+        <v>45900.35040481482</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Platens</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CA Platense – Godoy CruzLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>01/09 22:15</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45900.38834343067</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>01/09 22:15</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>55</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,142 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45900.38834343067</v>
+        <v>45900.38834342593</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Nacional A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nacional Asuncion – CD RecoletaPrimera Division</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>06/09 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+38,7%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45900.4306597981</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Leandro Ri</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Leandro Riedi – Alex De MinaurUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>01/09 15:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+24,1%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45900.4306597981</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Celta Vigo</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Celta Vigo – VillarrealEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+16,8%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45900.4306597981</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>06/09 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>50</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45900.4306597981</v>
+        <v>45900.43065980324</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>01/09 15:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>60</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45900.4306597981</v>
+        <v>45900.43065980324</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.7</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,97 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45900.4306597981</v>
+        <v>45900.43065980324</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ZSC Lions – Gorniczy Klub Sportowy TychyLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>31/08 13:45</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+154%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45900.4693808275</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 22.5 - tirs | Celta Vigo</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Celta Vigo – VillarrealEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+15,9%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45900.4693808275</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>31/08 13:45</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>175</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45900.4693808275</v>
+        <v>45900.46938082176</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F45" t="n">
+        <v>3.2</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,97 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45900.4693808275</v>
+        <v>45900.46938082176</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | UT Pétange</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UT Pétange – FC Progres NiederkornNational Division</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>31/08 14:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45900.52718253453</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 22.5 - tirs | Celta Vigo</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Celta Vigo – VillarrealLaLiga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+12,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45900.52718253453</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>31/08 14:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>35</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45900.52718253453</v>
+        <v>45900.52718253472</v>
       </c>
     </row>
     <row r="47">
@@ -2442,23 +2440,156 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+12,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45900.52718253472</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | M.Kostyuk </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>M.Kostyuk – K.MuchovaWTA - US Open F</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>01/09 19:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>59,9%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+13,7%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45900.55886650559</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 22.5 - tirs | Monaco – S</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Monaco – StrasbourgFrance - Ligue 1 McDonald’s®</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>31/08 15:15</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>37,4%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>+12,1%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>45900.52718253453</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+10,7%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45900.55886650559</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 11.5 - tirs2e équipe | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Lech Poznan – Widzew LodzPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>31/08 15:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52,3%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+8,89%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45900.55886650559</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>01/09 19:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F48" t="n">
+        <v>1.9</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45900.55886650559</v>
+        <v>45900.55886650463</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>31/08 15:15</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>3</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45900.55886650559</v>
+        <v>45900.55886650463</v>
       </c>
     </row>
     <row r="50">
@@ -2573,10 +2569,8 @@
           <t>31/08 15:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.08</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2589,7 +2583,232 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45900.55886650559</v>
+        <v>45900.55886650463</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 22.5 - tirs | Alanyaspor</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Alanyaspor – BesiktasTurquie - Turquie Super Lig</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>31/08 18:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>43,2%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+16,6%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45900.59567473143</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Italie – E</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Italie – EstonieCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>05/09 18:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45900.59567473143</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Genoa – Ju</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Genoa – JuventusItalie - Italie Serie A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>31/08 16:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+9,48%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45900.59567473143</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 16.5 - tirs1re équipe | Jagielloni</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystok – Lechia GdanskPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>31/08 15:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>49,4%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+8,72%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45900.59567473143</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Indiana Fe</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Indiana Fever – Golden State ValkyriesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>01/09 00:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+8,22%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45900.59567473143</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>31/08 18:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.7</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45900.59567473143</v>
+        <v>45900.5956747338</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>05/09 18:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>55</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45900.59567473143</v>
+        <v>45900.5956747338</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>31/08 16:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F53" t="n">
+        <v>3.7</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45900.59567473143</v>
+        <v>45900.5956747338</v>
       </c>
     </row>
     <row r="54">
@@ -2747,10 +2741,8 @@
           <t>31/08 15:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F54" t="n">
+        <v>2.2</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2763,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45900.59567473143</v>
+        <v>45900.5956747338</v>
       </c>
     </row>
     <row r="55">
@@ -2792,10 +2784,8 @@
           <t>01/09 00:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>25</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2808,7 +2798,322 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45900.59567473143</v>
+        <v>45900.5956747338</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | Alanyaspor</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Alanyaspor – BesiktasTurquie - Turquie Super Lig</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>31/08 18:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+16,5%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45900.63841339644</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 12.5 - tirs1re équipe | Liverpool </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Liverpool – ArsenalAngleterre - Angl. Premier League</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>31/08 15:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>40,5%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+9,36%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45900.63841339644</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | AugerAlias</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AugerAliassime – A.RublevATP - US Open H</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>01/09 15:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+7,85%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45900.63841339644</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set2e participant | Chandrasek</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chandrasekar A/Prashanth N – S - Romboli F/Smith J-PUS Open - Doubles (H)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>31/08 20:10</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+7,64%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45900.63841339644</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 20.5 - tirs | Genoa – Ju</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Genoa – JuventusItalie - Italie Serie A</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 20.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>31/08 16:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+7,58%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45900.63841339644</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs2e équipe | KS Cracovi</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>KS Cracovia – Legia VarsoviePologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>31/08 18:15</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>45,9%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+7,03%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45900.63841339644</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | Borussia D</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund – Union BerlinAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>31/08 15:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+6,75%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45900.63841339644</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>31/08 18:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45900.63841339644</v>
+        <v>45900.63841339121</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>31/08 15:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F57" t="n">
+        <v>2.7</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45900.63841339644</v>
+        <v>45900.63841339121</v>
       </c>
     </row>
     <row r="58">
@@ -2917,10 +2913,8 @@
           <t>01/09 15:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F58" t="n">
+        <v>1.55</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2933,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45900.63841339644</v>
+        <v>45900.63841339121</v>
       </c>
     </row>
     <row r="59">
@@ -2962,10 +2956,8 @@
           <t>31/08 20:10</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
+      <c r="F59" t="n">
+        <v>4.7</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2978,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45900.63841339644</v>
+        <v>45900.63841339121</v>
       </c>
     </row>
     <row r="60">
@@ -3007,10 +2999,8 @@
           <t>31/08 16:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.3</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3023,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45900.63841339644</v>
+        <v>45900.63841339121</v>
       </c>
     </row>
     <row r="61">
@@ -3052,10 +3042,8 @@
           <t>31/08 18:15</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.33</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3068,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45900.63841339644</v>
+        <v>45900.63841339121</v>
       </c>
     </row>
     <row r="62">
@@ -3097,10 +3085,8 @@
           <t>31/08 15:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3113,7 +3099,187 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45900.63841339644</v>
+        <v>45900.63841339121</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Pumas Unam</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Pumas Unam – Atlas FC385076e7 Liga MX</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>31/08 22:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,40%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+8,15%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45900.68322049438</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | A.Anisimov</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A.Anisimova – B.Haddad MaiaWTA - US Open F</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>01/09 15:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>73,2%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+6,15%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45900.68322049438</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | H 1 (+4.5) | Williams/W</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Williams/Winegar – Krawietz/PuetzUS Open 2025 - Hommes</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>H 1 (+4.5)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>01/09 14:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>55,8%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+4,85%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45900.68322049438</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 3.51er set1er participant | Kostyuk M/</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Kostyuk M/Ruse E – Haddad Maia B/Siegemund LUS Open - Doubles (F)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Moins que 3.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>31/08 19:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>36,7%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+4,58%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45900.68322049438</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>31/08 22:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>45</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45900.68322049438</v>
+        <v>45900.68322049768</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>01/09 15:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="F64" t="n">
+        <v>1.45</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45900.68322049438</v>
+        <v>45900.68322049768</v>
       </c>
     </row>
     <row r="65">
@@ -3218,10 +3214,8 @@
           <t>01/09 14:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
+      <c r="F65" t="n">
+        <v>1.88</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45900.68322049438</v>
+        <v>45900.68322049768</v>
       </c>
     </row>
     <row r="66">
@@ -3263,10 +3257,8 @@
           <t>31/08 19:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F66" t="n">
+        <v>2.85</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3279,7 +3271,142 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45900.68322049438</v>
+        <v>45900.68322049768</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Inter Mila</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Inter Milan – UdineseItalie - Italie Serie A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>31/08 18:45</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+10,6%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45900.71997793735</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tir cadré | Los Angele</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Los Angeles FC – San Diego FCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>01/09 02:45</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>27,3%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+3,83%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45900.71997793735</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Lyon – Mar</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Lyon – MarseilleFrance - Ligue 1 McDonald’s®</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>31/08 18:45</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+3,52%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45900.71997793735</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>31/08 18:45</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45900.71997793735</v>
+        <v>45900.71997793981</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>01/09 02:45</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="F68" t="n">
+        <v>3.8</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45900.71997793735</v>
+        <v>45900.71997793981</v>
       </c>
     </row>
     <row r="69">
@@ -3390,10 +3386,8 @@
           <t>31/08 18:45</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F69" t="n">
+        <v>3.3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3406,7 +3400,322 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45900.71997793735</v>
+        <v>45900.71997793981</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | Moins que 5.5 - break | A.Sabalenk</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A.Sabalenka – C.BucsaWTA - US Open F</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Moins que 5.5 - break</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>31/08 21:20</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>54,9%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+9,79%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45900.7691969416</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 21.5 - tirs | Los Angele</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Los Angeles FC – San Diego FCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Moins que 21.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>01/09 02:45</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+3,96%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45900.7691969416</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Plus que 6.51er set1er participant | Erler A / </t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Erler A / Galloway R – Schnaitter J/Wallner MUS Open - Doubles (H)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>31/08 20:40</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+2,95%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45900.7691969416</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | H 1 (+4.5) | Mcdonald/Q</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mcdonald/Quinn – Granollers/ZeballosUS Open 2025 - Hommes</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>H 1 (+4.5)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>01/09 14:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>59,3%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+1,93%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45900.7691969416</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Mirassol – Bahia Salvador BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>31/08 21:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>28,2%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+1,55%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45900.7691969416</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Tennis | Moins que 8.51er set | Rybakina, </t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Rybakina, Elena – Vondrousova, MarketaEvénements. US Open (F)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Moins que 8.51er set</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>01/09 01:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+1,47%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45900.7691969416</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Union Magd</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Union Magdalena – Atletico JuniorPrimera A</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>06/09 23:20</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+1,26%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45900.7691969416</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3429,10 +3429,8 @@
           <t>31/08 21:20</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3445,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45900.7691969416</v>
+        <v>45900.76919694444</v>
       </c>
     </row>
     <row r="71">
@@ -3474,10 +3472,8 @@
           <t>01/09 02:45</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F71" t="n">
+        <v>2.65</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3490,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45900.7691969416</v>
+        <v>45900.76919694444</v>
       </c>
     </row>
     <row r="72">
@@ -3519,10 +3515,8 @@
           <t>31/08 20:40</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
+      <c r="F72" t="n">
+        <v>4.7</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3535,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45900.7691969416</v>
+        <v>45900.76919694444</v>
       </c>
     </row>
     <row r="73">
@@ -3564,10 +3558,8 @@
           <t>01/09 14:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F73" t="n">
+        <v>1.72</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3580,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45900.7691969416</v>
+        <v>45900.76919694444</v>
       </c>
     </row>
     <row r="74">
@@ -3609,10 +3601,8 @@
           <t>31/08 21:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F74" t="n">
+        <v>3.6</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3625,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45900.7691969416</v>
+        <v>45900.76919694444</v>
       </c>
     </row>
     <row r="75">
@@ -3654,10 +3644,8 @@
           <t>01/09 01:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F75" t="n">
+        <v>3.5</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3670,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45900.7691969416</v>
+        <v>45900.76919694444</v>
       </c>
     </row>
     <row r="76">
@@ -3699,23 +3687,156 @@
           <t>06/09 23:20</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="n">
+        <v>40</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+1,26%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45900.76919694444</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Rayo Valle</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano – BarceloneEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>31/08 19:30</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+5,20%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45900.80284808538</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Santa Fe –</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Santa Fe – Once CaldasPrimera A</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>02/09 00:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>+1,26%</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>45900.7691969416</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+2,48%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45900.80284808538</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis | Moins que 1.5 - break2e participant | Novak Djok</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Novak Djokovic – Jan-Lennard StruffUS Open H.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Moins que 1.5 - break2e participant</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>31/08 23:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+2,12%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45900.80284808538</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,10 +3730,8 @@
           <t>31/08 19:30</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F77" t="n">
+        <v>3.2</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3746,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45900.80284808538</v>
+        <v>45900.80284809028</v>
       </c>
     </row>
     <row r="78">
@@ -3775,10 +3773,8 @@
           <t>02/09 00:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>40</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3791,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45900.80284808538</v>
+        <v>45900.80284809028</v>
       </c>
     </row>
     <row r="79">
@@ -3820,10 +3816,8 @@
           <t>31/08 23:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="F79" t="n">
+        <v>2.05</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3836,7 +3830,142 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45900.80284808538</v>
+        <v>45900.80284809028</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Club Gener</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Club General Caballero JLM – Libertad AsuncionPrimera Division</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>06/09 21:30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2,80%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+39,8%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45900.84849952544</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | H 2 (−7.5) | Machac, To</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Machac, Tomas – Fritz, TaylorEvénements. US Open (H)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>H 2 (−7.5)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>31/08 20:30</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>19,8%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+7,04%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45900.84849952544</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X1re période[race to 15 regular time] | Indiana Fe</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Indiana Fever – Golden State ValkyriesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>X1re période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>01/09 00:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+2,42%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45900.84849952544</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3859,10 +3859,8 @@
           <t>06/09 21:30</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>50</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3875,7 +3873,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45900.84849952544</v>
+        <v>45900.84849952546</v>
       </c>
     </row>
     <row r="81">
@@ -3904,10 +3902,8 @@
           <t>31/08 20:30</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
+      <c r="F81" t="n">
+        <v>5.4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3920,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45900.84849952544</v>
+        <v>45900.84849952546</v>
       </c>
     </row>
     <row r="82">
@@ -3949,10 +3945,8 @@
           <t>01/09 00:00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F82" t="n">
+        <v>40</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3965,7 +3959,187 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45900.84849952544</v>
+        <v>45900.84849952546</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Club OlimpiaPrimera Division</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>07/09 19:00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+21,2%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45900.88759507518</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Corinthian</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Corinthians – PalmeirasSérie A</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>31/08 21:30</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+15,6%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45900.88759507518</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Jiri Lehec</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka – Carlos AlcarazUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>02/09 15:30</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45900.88759507518</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 2.51re équipe | Arménie – </t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Arménie – PortugalCDM - Qualifs Europe</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>06/09 16:00</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+0,63%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45900.88759507518</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3988,10 +3988,8 @@
           <t>07/09 19:00</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F83" t="n">
+        <v>45</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4004,7 +4002,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45900.88759507518</v>
+        <v>45900.88759506944</v>
       </c>
     </row>
     <row r="84">
@@ -4033,10 +4031,8 @@
           <t>31/08 21:30</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F84" t="n">
+        <v>50</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4049,7 +4045,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45900.88759507518</v>
+        <v>45900.88759506944</v>
       </c>
     </row>
     <row r="85">
@@ -4078,10 +4074,8 @@
           <t>02/09 15:30</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F85" t="n">
+        <v>55</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4094,7 +4088,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45900.88759507518</v>
+        <v>45900.88759506944</v>
       </c>
     </row>
     <row r="86">
@@ -4123,23 +4117,111 @@
           <t>06/09 16:00</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" t="n">
+        <v>50</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+0,63%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45900.88759506944</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Basketball | 21-2P | Allemagne </t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Allemagne – Grande-BretagneEurope - EuroBasket</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>21-2P</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>01/09 13:30</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>+0,63%</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>45900.88759507518</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+17,6%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45900.93005221837</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | 11re période | Dallas Win</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Dallas Wings – Minnesota LynxUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>11re période</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02/09 00:00</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>+2,08%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45900.93005221837</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-31.xlsx
+++ b/data/valuebets_database_2025-08-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4160,10 +4160,8 @@
           <t>01/09 13:30</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F87" t="n">
+        <v>50</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4176,7 +4174,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45900.93005221837</v>
+        <v>45900.93005222223</v>
       </c>
     </row>
     <row r="88">
@@ -4205,10 +4203,8 @@
           <t>02/09 00:00</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F88" t="n">
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4221,7 +4217,187 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45900.93005221837</v>
+        <v>45900.93005222223</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Internacional – FortalezaSérie A</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>31/08 23:30</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>+41,9%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>45900.97161718587</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | 21-2P | Serbie – R</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Serbie – République TchèqueEurope - EuroBasket</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>21-2P</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>01/09 18:15</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>42.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>+11,5%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>45900.97161718587</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Atlanta Dr</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Atlanta Dream – Connecticut SunUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>01/09 17:00</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>+1,84%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>45900.97161718587</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Basketball | 11-2P | Finlande –</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Finlande – LituanieEurope - Eurobasket H.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>11-2P</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>01/09 17:30</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>+0,42%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>45900.97161718587</v>
       </c>
     </row>
   </sheetData>
